--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_150/per_file_predictions_epoch_150.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run7/epoch_150/per_file_predictions_epoch_150.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="501">
   <si>
     <t>Filename</t>
   </si>
@@ -808,700 +808,715 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9846,0.0023,0.0045,0.0011</t>
-  </si>
-  <si>
-    <t>0.0014,0.0000,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.9873,0.0061,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0544,0.0000,0.0001,0.9918</t>
+    <t>0.9964,0.0006,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0000,0.0000,0.9992</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9976,0.0020,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0015,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0040,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0214,0.0173,0.9442,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.0002,0.9971,0.0001</t>
+  </si>
+  <si>
+    <t>0.0652,0.0011,0.9548,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0003</t>
+  </si>
+  <si>
+    <t>0.9960,0.0003,0.0023,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0060,0.9929,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9761,0.0002,0.0217,0.0001</t>
+  </si>
+  <si>
+    <t>0.9848,0.0007,0.0101,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9983,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.0004,0.9985,0.0005</t>
+  </si>
+  <si>
+    <t>0.0174,0.0001,0.9909,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.1423,0.8535,0.0031,0.0002</t>
+  </si>
+  <si>
+    <t>0.4634,0.0245,0.3617,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9997,0.0035</t>
+  </si>
+  <si>
+    <t>0.0021,0.9931,0.0054,0.0000</t>
+  </si>
+  <si>
+    <t>0.9898,0.0071,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9955,0.0013,0.0014,0.0005</t>
+  </si>
+  <si>
+    <t>0.1221,0.9199,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.9896,0.0034,0.0008</t>
+  </si>
+  <si>
+    <t>0.0078,0.9533,0.0545,0.0040</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9969,0.0009</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9993,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0123,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0122,0.9448,0.0168,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9171,0.0009,0.8155</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0264,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.0007,0.9944,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0005,0.9990,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0020,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.9830,0.0175,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0008,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9894,0.0040,0.0023,0.0016</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9983,0.9660,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0007,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9611,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.9983,0.0018,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9798,0.0026,0.0159,0.0000</t>
+  </si>
+  <si>
+    <t>0.9561,0.0368,0.0038,0.0005</t>
+  </si>
+  <si>
+    <t>0.0005,0.0007,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9988,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9962,0.9329,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.8795,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.9847,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0010,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0004,0.9996</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0001,0.9998</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0002,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9995,0.7552,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9994,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9936,0.9834,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.6075,0.9993,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9943,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9980,0.9237,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0018,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0088,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9990,0.0006,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9974,0.0013,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9929,0.0106,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9949,0.0063,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0144,0.0267,0.9607,0.0002</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.9978,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9642,0.0464,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9338,0.0027,0.0375,0.0005</t>
+  </si>
+  <si>
+    <t>0.9438,0.0002,0.0766,0.0000</t>
+  </si>
+  <si>
+    <t>0.0686,0.8806,0.0147,0.0005</t>
+  </si>
+  <si>
+    <t>0.9137,0.0008,0.0831,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0053,0.0003,0.9987</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.5149,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.8323,0.1895,0.0038,0.0002</t>
+  </si>
+  <si>
+    <t>0.3577,0.5473,0.0237,0.0007</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0011,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0027,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9772,0.0175,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9990,0.0009,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0740,0.0102,0.8871,0.0002</t>
-  </si>
-  <si>
-    <t>0.0074,0.0052,0.9883,0.0004</t>
-  </si>
-  <si>
-    <t>0.9390,0.0002,0.0992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0002,0.0012,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9987,0.0020,0.0000</t>
-  </si>
-  <si>
-    <t>0.8432,0.1911,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9811,0.0001,0.0181,0.0001</t>
-  </si>
-  <si>
-    <t>0.1271,0.0001,0.8964,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9980,0.0005</t>
-  </si>
-  <si>
-    <t>0.0082,0.0009,0.9913,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9996,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0518,0.9597,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9811,0.0087,0.0038,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0004,0.9980,0.0028</t>
-  </si>
-  <si>
-    <t>0.0058,0.9631,0.0289,0.0001</t>
-  </si>
-  <si>
-    <t>0.9891,0.0119,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.2411,0.0111,0.7600,0.0023</t>
-  </si>
-  <si>
-    <t>0.0171,0.9823,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0029,0.9927,0.0014,0.0014</t>
-  </si>
-  <si>
-    <t>0.0140,0.8714,0.0925,0.0049</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9989,0.0012</t>
-  </si>
-  <si>
-    <t>0.0048,0.0016,0.9913,0.0003</t>
-  </si>
-  <si>
-    <t>0.1312,0.0000,0.8997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0007,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0032,0.9935,0.0028,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.8289,0.0003,0.9185</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0015,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0778,0.9986,0.0000</t>
-  </si>
-  <si>
-    <t>0.0262,0.0002,0.9783,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0000,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0086,0.0008,0.9934,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9937,0.0010,0.0031,0.0010</t>
-  </si>
-  <si>
-    <t>0.9982,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.9938,0.0021,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9988,0.0007,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9981,0.0009,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9973,0.9669,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9979,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0014,0.9978,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.3459,0.0053,0.7400,0.0000</t>
-  </si>
-  <si>
-    <t>0.4199,0.1274,0.1553,0.0008</t>
-  </si>
-  <si>
-    <t>0.0000,0.0028,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.8001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.6128,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.9713,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0349,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.0006,0.9997</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0002,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.4958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9926,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9520,0.9837,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9079,0.9979,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9987,0.9885,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.9689,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0067,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0007,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0012,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9965,0.0021,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.9941,0.0084,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9973,0.0027,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0002</t>
+    <t>0.9985,0.0002,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9983,0.0003,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0003,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0005,0.0002,0.0013</t>
+  </si>
+  <si>
+    <t>0.9986,0.0002,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.0000,0.5452,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9770,0.9960,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0232,0.9981,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3195,0.0383,0.5233,0.0033</t>
+  </si>
+  <si>
+    <t>0.0247,0.0002,0.9839,0.0001</t>
+  </si>
+  <si>
+    <t>0.9039,0.0051,0.0438,0.0019</t>
+  </si>
+  <si>
+    <t>0.1001,0.0000,0.0000,0.9765</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9898,0.9941,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0109,0.9816,0.0022,0.0065</t>
+  </si>
+  <si>
+    <t>0.9988,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.1156,0.8678,0.0082,0.0005</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0035,0.0000,0.0025,0.9975</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.0000,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0000,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9997,0.0005</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.9972,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.9602,0.0474,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.3237,0.0106,0.5638,0.0004</t>
-  </si>
-  <si>
-    <t>0.9610,0.0004,0.0412,0.0000</t>
-  </si>
-  <si>
-    <t>0.2326,0.6897,0.0077,0.0011</t>
-  </si>
-  <si>
-    <t>0.6448,0.0017,0.3523,0.0007</t>
-  </si>
-  <si>
-    <t>0.0003,0.0097,0.0035,0.9907</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0011</t>
-  </si>
-  <si>
-    <t>0.0002,0.9992,0.0120,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9994,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.3723,0.6423,0.0056,0.0002</t>
-  </si>
-  <si>
-    <t>0.8136,0.1619,0.0063,0.0004</t>
-  </si>
-  <si>
-    <t>0.9982,0.0009,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9962,0.0009,0.0011,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9985,0.0003,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.7446,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6107,0.9944,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0050,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0003,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.6841,0.0015,0.3427,0.0007</t>
-  </si>
-  <si>
-    <t>0.0116,0.0001,0.9910,0.0001</t>
-  </si>
-  <si>
-    <t>0.9966,0.0002,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0786,0.0000,0.0000,0.9851</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9977,0.9740,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0140,0.9803,0.0020,0.0023</t>
-  </si>
-  <si>
-    <t>0.9988,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.0179,0.9773,0.0056,0.0003</t>
-  </si>
-  <si>
-    <t>0.9985,0.0000,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.0065,0.0000,0.0002,0.9984</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0135,0.0301,0.9809,0.0019</t>
-  </si>
-  <si>
-    <t>0.9914,0.0001,0.0033,0.0013</t>
-  </si>
-  <si>
-    <t>0.9924,0.0012,0.0022,0.0022</t>
-  </si>
-  <si>
-    <t>0.2004,0.7701,0.0066,0.0003</t>
-  </si>
-  <si>
-    <t>0.9843,0.0066,0.0017,0.0005</t>
-  </si>
-  <si>
-    <t>0.9890,0.0090,0.0004,0.0002</t>
-  </si>
-  <si>
-    <t>0.1121,0.8996,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.3997,0.0512,0.2732,0.0016</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0001,0.0008</t>
-  </si>
-  <si>
-    <t>0.9985,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0004,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9919,0.0054,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.4952,0.6105,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.4745,0.5564,0.0042,0.0001</t>
-  </si>
-  <si>
-    <t>0.5827,0.4663,0.0021,0.0000</t>
-  </si>
-  <si>
-    <t>0.9730,0.0153,0.0080,0.0009</t>
-  </si>
-  <si>
-    <t>0.9975,0.0023,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9968,0.0009,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.9965,0.0015,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.8443,0.2022,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.9236,0.0346,0.0330,0.0033</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0005,0.9987,0.0013</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0417,0.0011,0.9748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.0015,0.9917,0.0002</t>
-  </si>
-  <si>
-    <t>0.0439,0.0016,0.9575,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0011,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0056,0.9904,0.0003</t>
-  </si>
-  <si>
-    <t>0.0253,0.0033,0.9662,0.0003</t>
-  </si>
-  <si>
-    <t>0.9086,0.0031,0.0763,0.0004</t>
-  </si>
-  <si>
-    <t>0.9176,0.0009,0.0789,0.0006</t>
-  </si>
-  <si>
-    <t>0.0390,0.0007,0.9662,0.0003</t>
-  </si>
-  <si>
-    <t>0.0133,0.9900,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0824,0.9407,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.0351,0.9726,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0083,0.9920,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.4736,0.5551,0.0014,0.0004</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0024,0.0000</t>
-  </si>
-  <si>
-    <t>0.9279,0.0021,0.0340,0.0065</t>
-  </si>
-  <si>
-    <t>0.9735,0.0007,0.0192,0.0002</t>
-  </si>
-  <si>
-    <t>0.6261,0.0003,0.4442,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0115,0.0099,0.9706,0.0012</t>
-  </si>
-  <si>
-    <t>0.0036,0.2062,0.9312,0.0002</t>
-  </si>
-  <si>
-    <t>0.0019,0.0007,0.9955,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0020,0.9981,0.0002</t>
-  </si>
-  <si>
-    <t>0.9985,0.0004,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9972,0.0013,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9961,0.0020,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9869,0.0143,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0027,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0017,0.9998,0.0012</t>
-  </si>
-  <si>
-    <t>0.0085,0.9628,0.0305,0.0006</t>
-  </si>
-  <si>
-    <t>0.7777,0.0002,0.1613,0.0035</t>
-  </si>
-  <si>
-    <t>0.0009,0.0005,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0144,0.9932,0.0002</t>
+    <t>0.1661,0.0206,0.8465,0.0015</t>
+  </si>
+  <si>
+    <t>0.9981,0.0001,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9919,0.0010,0.0008,0.0043</t>
+  </si>
+  <si>
+    <t>0.8719,0.1309,0.0024,0.0002</t>
+  </si>
+  <si>
+    <t>0.9953,0.0012,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.7721,0.2028,0.0029,0.0048</t>
+  </si>
+  <si>
+    <t>0.0519,0.9387,0.0032,0.0003</t>
+  </si>
+  <si>
+    <t>0.9167,0.0077,0.0485,0.0003</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.9948,0.0030,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9940,0.0006,0.0026,0.0010</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9914,0.0040,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.1656,0.8638,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.8683,0.1110,0.0073,0.0001</t>
+  </si>
+  <si>
+    <t>0.0223,0.9617,0.0083,0.0002</t>
+  </si>
+  <si>
+    <t>0.1444,0.1034,0.7676,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0028,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9898,0.0073,0.0013,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.4791,0.6084,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9911,0.0033,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0076,0.0002,0.9950,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9998,0.0000</t>
   </si>
   <si>
     <t>0.0000,0.0001,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.0001,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0112,0.0000,0.9953,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.1332,0.9880,0.0008</t>
-  </si>
-  <si>
-    <t>0.9897,0.0001,0.0096,0.0000</t>
-  </si>
-  <si>
-    <t>0.1495,0.0004,0.8610,0.0006</t>
-  </si>
-  <si>
-    <t>0.9908,0.0001,0.0077,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0019,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0059,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9983,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0196,0.0023,0.9673,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0040,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0102,0.1569,0.6410,0.0030</t>
-  </si>
-  <si>
-    <t>0.0047,0.0041,0.9830,0.0003</t>
+    <t>0.0195,0.1027,0.7135,0.0004</t>
+  </si>
+  <si>
+    <t>0.0021,0.0004,0.9973,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0020,0.9956,0.0002</t>
+  </si>
+  <si>
+    <t>0.0888,0.0035,0.9099,0.0002</t>
+  </si>
+  <si>
+    <t>0.3129,0.0058,0.6953,0.0002</t>
+  </si>
+  <si>
+    <t>0.9081,0.0032,0.0722,0.0003</t>
+  </si>
+  <si>
+    <t>0.9742,0.0006,0.0187,0.0003</t>
+  </si>
+  <si>
+    <t>0.0682,0.0108,0.8839,0.0042</t>
+  </si>
+  <si>
+    <t>0.0012,0.9985,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0026,0.9975,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0331,0.9723,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0104,0.9907,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0018,0.9977,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9867,0.0113,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.8980,0.0017,0.0556,0.0067</t>
+  </si>
+  <si>
+    <t>0.9603,0.0005,0.0382,0.0002</t>
+  </si>
+  <si>
+    <t>0.9740,0.0004,0.0176,0.0004</t>
+  </si>
+  <si>
+    <t>0.0180,0.0712,0.9117,0.0032</t>
+  </si>
+  <si>
+    <t>0.0017,0.8586,0.8121,0.0002</t>
+  </si>
+  <si>
+    <t>0.0017,0.0002,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0026,0.9978,0.0002</t>
+  </si>
+  <si>
+    <t>0.9966,0.0019,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9968,0.0026,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9984,0.0020,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0019,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0030,0.9993,0.0009</t>
+  </si>
+  <si>
+    <t>0.0756,0.2978,0.2976,0.0035</t>
+  </si>
+  <si>
+    <t>0.8578,0.0001,0.0984,0.0031</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0516,0.0008,0.8846,0.0136</t>
-  </si>
-  <si>
-    <t>0.0043,0.0028,0.9923,0.0006</t>
-  </si>
-  <si>
-    <t>0.0141,0.0002,0.9803,0.0007</t>
-  </si>
-  <si>
-    <t>0.8876,0.0000,0.0010,0.1123</t>
-  </si>
-  <si>
-    <t>0.0002,0.0055,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.1661,0.0001,0.0026,0.9138</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.8555,0.0107,0.0026,0.0585</t>
+    <t>0.0000,0.0042,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0153,0.9985,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0024,0.0014,0.9948,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9988,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0269,0.9990,0.0012</t>
+  </si>
+  <si>
+    <t>0.9944,0.0000,0.0067,0.0000</t>
+  </si>
+  <si>
+    <t>0.9594,0.0000,0.0488,0.0001</t>
+  </si>
+  <si>
+    <t>0.9949,0.0002,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9964,0.0037,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0011,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9970,0.0018,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0056,0.0029,0.9816,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0073,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0020,0.0129,0.9759,0.0014</t>
+  </si>
+  <si>
+    <t>0.0058,0.0029,0.9823,0.0010</t>
+  </si>
+  <si>
+    <t>0.0031,0.0024,0.9899,0.0089</t>
+  </si>
+  <si>
+    <t>0.0211,0.0014,0.9756,0.0008</t>
+  </si>
+  <si>
+    <t>0.0166,0.0001,0.9802,0.0004</t>
+  </si>
+  <si>
+    <t>0.9528,0.0000,0.0019,0.0312</t>
+  </si>
+  <si>
+    <t>0.0001,0.0097,0.0000,0.9996</t>
+  </si>
+  <si>
+    <t>0.0384,0.0006,0.0020,0.9863</t>
+  </si>
+  <si>
+    <t>0.7993,0.0193,0.0047,0.0737</t>
   </si>
 </sst>
 </file>
@@ -1887,7 +1902,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1901,7 +1916,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1915,7 +1930,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1929,7 +1944,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1943,7 +1958,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1957,7 +1972,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1971,7 +1986,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1985,7 +2000,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1999,7 +2014,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2013,7 +2028,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2027,7 +2042,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2041,7 +2056,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2055,7 +2070,7 @@
         <v>261</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2069,7 +2084,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2080,10 +2095,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2097,7 +2112,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2111,7 +2126,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2125,7 +2140,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2139,7 +2154,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2150,10 +2165,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2167,7 +2182,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2181,7 +2196,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2195,7 +2210,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2206,10 +2221,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2223,7 +2238,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2237,7 +2252,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2251,7 +2266,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2265,7 +2280,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2279,7 +2294,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2293,7 +2308,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2304,10 +2319,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2321,7 +2336,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2335,7 +2350,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2349,7 +2364,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2360,10 +2375,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2377,7 +2392,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2391,7 +2406,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2405,7 +2420,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2419,7 +2434,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2433,7 +2448,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2447,7 +2462,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2461,7 +2476,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2475,7 +2490,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2489,7 +2504,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2500,10 +2515,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2517,7 +2532,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2531,7 +2546,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2545,7 +2560,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2559,7 +2574,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2573,7 +2588,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2587,7 +2602,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2601,7 +2616,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2615,7 +2630,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2629,7 +2644,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2643,7 +2658,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2657,7 +2672,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2671,7 +2686,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2685,7 +2700,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2699,7 +2714,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2713,7 +2728,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2727,7 +2742,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2741,7 +2756,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2755,7 +2770,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2769,7 +2784,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2783,7 +2798,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2797,7 +2812,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2811,7 +2826,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2825,7 +2840,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>286</v>
+        <v>333</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2836,10 +2851,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2853,7 +2868,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2867,7 +2882,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2881,7 +2896,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2895,7 +2910,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2909,7 +2924,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2923,7 +2938,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2937,7 +2952,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2951,7 +2966,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2965,7 +2980,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2979,7 +2994,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2993,7 +3008,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3007,7 +3022,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3018,10 +3033,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3035,7 +3050,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3049,7 +3064,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3063,7 +3078,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3077,7 +3092,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3091,7 +3106,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3105,7 +3120,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3119,7 +3134,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>269</v>
+        <v>354</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3133,7 +3148,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3147,7 +3162,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3161,7 +3176,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3175,7 +3190,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3189,7 +3204,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3203,7 +3218,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3217,7 +3232,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>355</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3231,7 +3246,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3245,7 +3260,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>355</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3259,7 +3274,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3273,7 +3288,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3287,7 +3302,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3301,7 +3316,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3315,7 +3330,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3329,7 +3344,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3343,7 +3358,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3357,7 +3372,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3371,7 +3386,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3385,7 +3400,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3399,7 +3414,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>311</v>
+        <v>368</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3413,7 +3428,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3427,7 +3442,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3441,7 +3456,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>286</v>
+        <v>371</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3455,7 +3470,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>311</v>
+        <v>287</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3469,7 +3484,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3480,10 +3495,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3497,7 +3512,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3511,7 +3526,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3525,7 +3540,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3539,7 +3554,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3553,7 +3568,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3567,7 +3582,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>286</v>
+        <v>378</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3581,7 +3596,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3592,10 +3607,10 @@
         <v>263</v>
       </c>
       <c r="C124" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3609,7 +3624,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3620,10 +3635,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3634,10 +3649,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3651,7 +3666,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3665,7 +3680,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3679,7 +3694,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3693,7 +3708,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3707,7 +3722,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3721,7 +3736,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3735,7 +3750,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3749,7 +3764,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3763,7 +3778,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3777,7 +3792,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3791,7 +3806,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3805,7 +3820,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3819,7 +3834,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3830,10 +3845,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3847,7 +3862,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3861,7 +3876,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3875,7 +3890,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3889,7 +3904,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3903,7 +3918,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3917,7 +3932,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3931,7 +3946,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3945,7 +3960,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3959,7 +3974,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3973,7 +3988,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3987,7 +4002,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4001,7 +4016,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4015,7 +4030,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4029,7 +4044,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4043,7 +4058,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4057,7 +4072,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4071,7 +4086,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4082,10 +4097,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4099,7 +4114,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4113,7 +4128,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4127,7 +4142,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4141,7 +4156,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4155,7 +4170,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4169,7 +4184,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4183,7 +4198,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4197,7 +4212,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4211,7 +4226,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4225,7 +4240,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4239,7 +4254,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4253,7 +4268,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>359</v>
+        <v>425</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4267,7 +4282,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4281,7 +4296,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4292,10 +4307,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4306,10 +4321,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4320,10 +4335,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4337,7 +4352,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4351,7 +4366,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4365,7 +4380,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4376,10 +4391,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D180" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4393,7 +4408,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4407,7 +4422,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4421,7 +4436,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>430</v>
+        <v>331</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4435,7 +4450,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4449,7 +4464,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>432</v>
+        <v>306</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4463,7 +4478,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4477,7 +4492,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4491,7 +4506,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>329</v>
+        <v>439</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4505,7 +4520,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4519,7 +4534,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4533,7 +4548,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4547,7 +4562,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4561,7 +4576,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4575,7 +4590,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4589,7 +4604,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4603,7 +4618,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4617,7 +4632,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4631,7 +4646,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4645,7 +4660,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4659,7 +4674,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4673,7 +4688,7 @@
         <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4687,7 +4702,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4698,10 +4713,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4715,7 +4730,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4729,7 +4744,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4743,7 +4758,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4757,7 +4772,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4771,7 +4786,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>452</v>
+        <v>294</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4785,7 +4800,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4796,10 +4811,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D210" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4813,7 +4828,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4827,7 +4842,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4841,7 +4856,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4855,7 +4870,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4869,7 +4884,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4883,7 +4898,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4897,7 +4912,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4911,7 +4926,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4925,7 +4940,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4939,7 +4954,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4953,7 +4968,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4964,10 +4979,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4981,7 +4996,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4995,7 +5010,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5009,7 +5024,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>430</v>
+        <v>475</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5023,7 +5038,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5037,7 +5052,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5051,7 +5066,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5065,7 +5080,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5079,7 +5094,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5093,7 +5108,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5107,7 +5122,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5118,10 +5133,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5135,7 +5150,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5149,7 +5164,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5163,7 +5178,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5177,7 +5192,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5191,7 +5206,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5205,7 +5220,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5219,7 +5234,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>481</v>
+        <v>489</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5233,7 +5248,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>482</v>
+        <v>271</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5247,7 +5262,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>272</v>
+        <v>361</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5261,7 +5276,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5275,7 +5290,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5289,7 +5304,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5303,7 +5318,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5317,7 +5332,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>487</v>
+        <v>331</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5331,7 +5346,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5345,7 +5360,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5359,7 +5374,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5373,7 +5388,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5387,7 +5402,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5401,7 +5416,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5415,7 +5430,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>494</v>
+        <v>342</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5429,7 +5444,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5443,7 +5458,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
